--- a/variants/esp32s3/diy/RiV_meshnode_s3_joystick/RiV_meshnode_s3_joystick_pinout.xlsx
+++ b/variants/esp32s3/diy/RiV_meshnode_s3_joystick/RiV_meshnode_s3_joystick_pinout.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -652,78 +652,93 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>I2C SDA / SCL</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>18 / 17</t>
-        </is>
+          <t>LCD_MISO/SDO</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>RTC PCF8563, BME280</t>
+          <t>ILI9341 only: connect to the shared MISO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>RTC_INT</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
+          <t>I2C SDA / SCL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>18 / 17</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>RTC PCF8563, BME280</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>NEOPIXEL</t>
+          <t>RTC_INT</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>WS2812 x8</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>BUZZER</t>
+          <t>NEOPIXEL</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>WS2812 x8</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>BATTERY_ADC</t>
+          <t>BUZZER</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>BATTERY_ADC</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>BOOT</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
